--- a/output/Hebei/承德市_news.xlsx
+++ b/output/Hebei/承德市_news.xlsx
@@ -1230,7 +1230,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1241,13 +1241,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1715,28 +1708,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1745,126 +1741,124 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2304,9 +2298,7 @@
       <c r="M2">
         <v>190</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
+      <c r="N2"/>
       <c r="O2" t="s">
         <v>25</v>
       </c>
@@ -2354,9 +2346,7 @@
       <c r="M3">
         <v>487</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
+      <c r="N3"/>
       <c r="O3" t="s">
         <v>32</v>
       </c>
@@ -2404,9 +2394,7 @@
       <c r="M4">
         <v>6</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
+      <c r="N4"/>
       <c r="O4" t="s">
         <v>41</v>
       </c>
@@ -2454,9 +2442,7 @@
       <c r="M5">
         <v>188</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
+      <c r="N5"/>
       <c r="O5" t="s">
         <v>46</v>
       </c>
@@ -2504,10 +2490,8 @@
       <c r="M6">
         <v>183</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="N6"/>
+      <c r="O6" s="2" t="s">
         <v>49</v>
       </c>
       <c r="P6" t="s">
@@ -2554,9 +2538,7 @@
       <c r="M7">
         <v>176</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
+      <c r="N7"/>
       <c r="O7" t="s">
         <v>51</v>
       </c>
@@ -2604,9 +2586,7 @@
       <c r="M8">
         <v>189</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
+      <c r="N8"/>
       <c r="O8" t="s">
         <v>53</v>
       </c>
@@ -2654,9 +2634,7 @@
       <c r="M9">
         <v>180</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
+      <c r="N9"/>
       <c r="O9" t="s">
         <v>58</v>
       </c>
@@ -2704,9 +2682,7 @@
       <c r="M10">
         <v>363</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
+      <c r="N10"/>
       <c r="O10" t="s">
         <v>63</v>
       </c>
@@ -2754,9 +2730,7 @@
       <c r="M11">
         <v>161</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
+      <c r="N11"/>
       <c r="O11" t="s">
         <v>67</v>
       </c>
@@ -2804,9 +2778,7 @@
       <c r="M12">
         <v>194</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
+      <c r="N12"/>
       <c r="O12" t="s">
         <v>71</v>
       </c>
@@ -2854,9 +2826,7 @@
       <c r="M13">
         <v>198</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
+      <c r="N13"/>
       <c r="O13" t="s">
         <v>75</v>
       </c>
@@ -2904,9 +2874,7 @@
       <c r="M14">
         <v>300</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
+      <c r="N14"/>
       <c r="O14" t="s">
         <v>79</v>
       </c>
@@ -2954,9 +2922,7 @@
       <c r="M15">
         <v>166</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
+      <c r="N15"/>
       <c r="O15" t="s">
         <v>83</v>
       </c>
@@ -3004,9 +2970,7 @@
       <c r="M16">
         <v>174</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
+      <c r="N16"/>
       <c r="O16" t="s">
         <v>87</v>
       </c>
@@ -3054,9 +3018,7 @@
       <c r="M17">
         <v>175</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
+      <c r="N17"/>
       <c r="O17" t="s">
         <v>91</v>
       </c>
@@ -3104,9 +3066,7 @@
       <c r="M18">
         <v>183</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
+      <c r="N18"/>
       <c r="O18" t="s">
         <v>95</v>
       </c>
@@ -3154,9 +3114,7 @@
       <c r="M19">
         <v>176</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
+      <c r="N19"/>
       <c r="O19" t="s">
         <v>98</v>
       </c>
@@ -3204,9 +3162,7 @@
       <c r="M20">
         <v>169</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
+      <c r="N20"/>
       <c r="O20" t="s">
         <v>101</v>
       </c>
@@ -3254,9 +3210,7 @@
       <c r="M21">
         <v>175</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
+      <c r="N21"/>
       <c r="O21" t="s">
         <v>104</v>
       </c>
@@ -3304,9 +3258,7 @@
       <c r="M22">
         <v>172</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
+      <c r="N22"/>
       <c r="O22" t="s">
         <v>107</v>
       </c>
@@ -3354,9 +3306,7 @@
       <c r="M23">
         <v>199</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
+      <c r="N23"/>
       <c r="O23" t="s">
         <v>111</v>
       </c>
@@ -3404,9 +3354,7 @@
       <c r="M24">
         <v>613</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
+      <c r="N24"/>
       <c r="O24" t="s">
         <v>115</v>
       </c>
@@ -3454,9 +3402,7 @@
       <c r="M25">
         <v>459</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
+      <c r="N25"/>
       <c r="O25" t="s">
         <v>118</v>
       </c>
@@ -3504,9 +3450,7 @@
       <c r="M26">
         <v>474</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
+      <c r="N26"/>
       <c r="O26" t="s">
         <v>123</v>
       </c>
@@ -3554,9 +3498,7 @@
       <c r="M27">
         <v>457</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
+      <c r="N27"/>
       <c r="O27" t="s">
         <v>126</v>
       </c>
@@ -3604,9 +3546,7 @@
       <c r="M28">
         <v>745</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
+      <c r="N28"/>
       <c r="O28" t="s">
         <v>129</v>
       </c>
@@ -3654,9 +3594,7 @@
       <c r="M29">
         <v>489</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
+      <c r="N29"/>
       <c r="O29" t="s">
         <v>133</v>
       </c>
@@ -3704,9 +3642,7 @@
       <c r="M30">
         <v>8</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
+      <c r="N30"/>
       <c r="O30" t="s">
         <v>137</v>
       </c>
@@ -3754,9 +3690,7 @@
       <c r="M31">
         <v>13</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
+      <c r="N31"/>
       <c r="O31" t="s">
         <v>141</v>
       </c>
@@ -3804,9 +3738,7 @@
       <c r="M32">
         <v>798</v>
       </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
+      <c r="N32"/>
       <c r="O32" t="s">
         <v>145</v>
       </c>
@@ -3854,9 +3786,7 @@
       <c r="M33">
         <v>14</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
+      <c r="N33"/>
       <c r="O33" t="s">
         <v>148</v>
       </c>
@@ -3904,9 +3834,7 @@
       <c r="M34">
         <v>16</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
+      <c r="N34"/>
       <c r="O34" t="s">
         <v>151</v>
       </c>
@@ -3954,9 +3882,7 @@
       <c r="M35">
         <v>636</v>
       </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
+      <c r="N35"/>
       <c r="O35" t="s">
         <v>155</v>
       </c>
@@ -4004,9 +3930,7 @@
       <c r="M36">
         <v>29</v>
       </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
+      <c r="N36"/>
       <c r="O36" t="s">
         <v>160</v>
       </c>
@@ -4054,9 +3978,7 @@
       <c r="M37">
         <v>52</v>
       </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
+      <c r="N37"/>
       <c r="O37" t="s">
         <v>163</v>
       </c>
@@ -4104,9 +4026,7 @@
       <c r="M38">
         <v>410</v>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
+      <c r="N38"/>
       <c r="O38" t="s">
         <v>169</v>
       </c>
@@ -4154,9 +4074,7 @@
       <c r="M39">
         <v>28</v>
       </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
+      <c r="N39"/>
       <c r="O39" t="s">
         <v>172</v>
       </c>
@@ -4204,9 +4122,7 @@
       <c r="M40">
         <v>31</v>
       </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
+      <c r="N40"/>
       <c r="O40" t="s">
         <v>175</v>
       </c>
@@ -4254,9 +4170,7 @@
       <c r="M41">
         <v>29</v>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
+      <c r="N41"/>
       <c r="O41" t="s">
         <v>178</v>
       </c>
@@ -4304,9 +4218,7 @@
       <c r="M42">
         <v>24</v>
       </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
+      <c r="N42"/>
       <c r="O42" t="s">
         <v>181</v>
       </c>
@@ -4354,9 +4266,7 @@
       <c r="M43">
         <v>58</v>
       </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
+      <c r="N43"/>
       <c r="O43" t="s">
         <v>184</v>
       </c>
@@ -4404,9 +4314,7 @@
       <c r="M44">
         <v>25</v>
       </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
+      <c r="N44"/>
       <c r="O44" t="s">
         <v>187</v>
       </c>
@@ -4454,9 +4362,7 @@
       <c r="M45">
         <v>24</v>
       </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
+      <c r="N45"/>
       <c r="O45" t="s">
         <v>190</v>
       </c>
@@ -4504,9 +4410,7 @@
       <c r="M46">
         <v>29</v>
       </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
+      <c r="N46"/>
       <c r="O46" t="s">
         <v>193</v>
       </c>
@@ -4554,9 +4458,7 @@
       <c r="M47">
         <v>21</v>
       </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
+      <c r="N47"/>
       <c r="O47" t="s">
         <v>197</v>
       </c>
@@ -4604,9 +4506,7 @@
       <c r="M48">
         <v>23</v>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
+      <c r="N48"/>
       <c r="O48" t="s">
         <v>200</v>
       </c>
@@ -4654,9 +4554,7 @@
       <c r="M49">
         <v>23</v>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
+      <c r="N49"/>
       <c r="O49" t="s">
         <v>203</v>
       </c>
@@ -4704,9 +4602,7 @@
       <c r="M50">
         <v>23</v>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
+      <c r="N50"/>
       <c r="O50" t="s">
         <v>206</v>
       </c>
@@ -4754,9 +4650,7 @@
       <c r="M51">
         <v>21</v>
       </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
+      <c r="N51"/>
       <c r="O51" t="s">
         <v>209</v>
       </c>
@@ -4804,9 +4698,7 @@
       <c r="M52">
         <v>32</v>
       </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
+      <c r="N52"/>
       <c r="O52" t="s">
         <v>212</v>
       </c>
@@ -4854,9 +4746,7 @@
       <c r="M53">
         <v>97</v>
       </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
+      <c r="N53"/>
       <c r="O53" t="s">
         <v>216</v>
       </c>
@@ -4904,9 +4794,7 @@
       <c r="M54">
         <v>30</v>
       </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
+      <c r="N54"/>
       <c r="O54" t="s">
         <v>220</v>
       </c>
@@ -4954,9 +4842,7 @@
       <c r="M55">
         <v>27</v>
       </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
+      <c r="N55"/>
       <c r="O55" t="s">
         <v>223</v>
       </c>
@@ -5004,9 +4890,7 @@
       <c r="M56">
         <v>31</v>
       </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
+      <c r="N56"/>
       <c r="O56" t="s">
         <v>226</v>
       </c>
@@ -5054,9 +4938,7 @@
       <c r="M57">
         <v>23</v>
       </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
+      <c r="N57"/>
       <c r="O57" t="s">
         <v>230</v>
       </c>
@@ -5104,9 +4986,7 @@
       <c r="M58">
         <v>31</v>
       </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
+      <c r="N58"/>
       <c r="O58" t="s">
         <v>233</v>
       </c>
@@ -5154,9 +5034,7 @@
       <c r="M59">
         <v>28</v>
       </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
+      <c r="N59"/>
       <c r="O59" t="s">
         <v>236</v>
       </c>
@@ -5204,9 +5082,7 @@
       <c r="M60">
         <v>28</v>
       </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
+      <c r="N60"/>
       <c r="O60" t="s">
         <v>239</v>
       </c>
@@ -5254,9 +5130,7 @@
       <c r="M61">
         <v>39</v>
       </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
+      <c r="N61"/>
       <c r="O61" t="s">
         <v>241</v>
       </c>
@@ -5304,9 +5178,7 @@
       <c r="M62">
         <v>30</v>
       </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
+      <c r="N62"/>
       <c r="O62" t="s">
         <v>244</v>
       </c>
@@ -5354,9 +5226,7 @@
       <c r="M63">
         <v>29</v>
       </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
+      <c r="N63"/>
       <c r="O63" t="s">
         <v>247</v>
       </c>
@@ -5404,9 +5274,7 @@
       <c r="M64">
         <v>25</v>
       </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
+      <c r="N64"/>
       <c r="O64" t="s">
         <v>250</v>
       </c>
@@ -5454,9 +5322,7 @@
       <c r="M65">
         <v>22</v>
       </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
+      <c r="N65"/>
       <c r="O65" t="s">
         <v>253</v>
       </c>
@@ -5504,9 +5370,7 @@
       <c r="M66">
         <v>23</v>
       </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
+      <c r="N66"/>
       <c r="O66" t="s">
         <v>256</v>
       </c>
@@ -5554,9 +5418,7 @@
       <c r="M67">
         <v>22</v>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
+      <c r="N67"/>
       <c r="O67" t="s">
         <v>259</v>
       </c>
@@ -5604,9 +5466,7 @@
       <c r="M68">
         <v>25</v>
       </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
+      <c r="N68"/>
       <c r="O68" t="s">
         <v>262</v>
       </c>
@@ -5654,9 +5514,7 @@
       <c r="M69">
         <v>43</v>
       </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
+      <c r="N69"/>
       <c r="O69" t="s">
         <v>266</v>
       </c>
@@ -5704,9 +5562,7 @@
       <c r="M70">
         <v>43</v>
       </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
+      <c r="N70"/>
       <c r="O70" t="s">
         <v>269</v>
       </c>
@@ -5754,9 +5610,7 @@
       <c r="M71">
         <v>32</v>
       </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
+      <c r="N71"/>
       <c r="O71" t="s">
         <v>272</v>
       </c>
@@ -5804,9 +5658,7 @@
       <c r="M72">
         <v>22</v>
       </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
+      <c r="N72"/>
       <c r="O72" t="s">
         <v>275</v>
       </c>
@@ -5854,9 +5706,7 @@
       <c r="M73">
         <v>21</v>
       </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
+      <c r="N73"/>
       <c r="O73" t="s">
         <v>278</v>
       </c>
@@ -5904,9 +5754,7 @@
       <c r="M74">
         <v>21</v>
       </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
+      <c r="N74"/>
       <c r="O74" t="s">
         <v>281</v>
       </c>
@@ -5954,9 +5802,7 @@
       <c r="M75">
         <v>29</v>
       </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
+      <c r="N75"/>
       <c r="O75" t="s">
         <v>284</v>
       </c>
@@ -6004,9 +5850,7 @@
       <c r="M76">
         <v>28</v>
       </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
+      <c r="N76"/>
       <c r="O76" t="s">
         <v>287</v>
       </c>
@@ -6054,9 +5898,7 @@
       <c r="M77">
         <v>27</v>
       </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
+      <c r="N77"/>
       <c r="O77" t="s">
         <v>290</v>
       </c>
@@ -6104,9 +5946,7 @@
       <c r="M78">
         <v>23</v>
       </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
+      <c r="N78"/>
       <c r="O78" t="s">
         <v>293</v>
       </c>
@@ -6154,9 +5994,7 @@
       <c r="M79">
         <v>76</v>
       </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
+      <c r="N79"/>
       <c r="O79" t="s">
         <v>297</v>
       </c>
@@ -6204,9 +6042,7 @@
       <c r="M80">
         <v>43</v>
       </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
+      <c r="N80"/>
       <c r="O80" t="s">
         <v>300</v>
       </c>
@@ -6254,9 +6090,7 @@
       <c r="M81">
         <v>29</v>
       </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
+      <c r="N81"/>
       <c r="O81" t="s">
         <v>303</v>
       </c>
@@ -6304,9 +6138,7 @@
       <c r="M82">
         <v>26</v>
       </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
+      <c r="N82"/>
       <c r="O82" t="s">
         <v>305</v>
       </c>
@@ -6354,9 +6186,7 @@
       <c r="M83">
         <v>22</v>
       </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
+      <c r="N83"/>
       <c r="O83" t="s">
         <v>308</v>
       </c>
@@ -6404,9 +6234,7 @@
       <c r="M84">
         <v>23</v>
       </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
+      <c r="N84"/>
       <c r="O84" t="s">
         <v>311</v>
       </c>
@@ -6454,9 +6282,7 @@
       <c r="M85">
         <v>26</v>
       </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
+      <c r="N85"/>
       <c r="O85" t="s">
         <v>314</v>
       </c>
@@ -6504,9 +6330,7 @@
       <c r="M86">
         <v>21</v>
       </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
+      <c r="N86"/>
       <c r="O86" t="s">
         <v>317</v>
       </c>
@@ -6554,9 +6378,7 @@
       <c r="M87">
         <v>27</v>
       </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
+      <c r="N87"/>
       <c r="O87" t="s">
         <v>320</v>
       </c>
@@ -6604,9 +6426,7 @@
       <c r="M88">
         <v>21</v>
       </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
+      <c r="N88"/>
       <c r="O88" t="s">
         <v>323</v>
       </c>
@@ -6654,9 +6474,7 @@
       <c r="M89">
         <v>24</v>
       </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
+      <c r="N89"/>
       <c r="O89" t="s">
         <v>326</v>
       </c>
@@ -6704,9 +6522,7 @@
       <c r="M90">
         <v>21</v>
       </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
+      <c r="N90"/>
       <c r="O90" t="s">
         <v>329</v>
       </c>
@@ -6754,9 +6570,7 @@
       <c r="M91">
         <v>22</v>
       </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
+      <c r="N91"/>
       <c r="O91" t="s">
         <v>332</v>
       </c>
@@ -6804,9 +6618,7 @@
       <c r="M92">
         <v>23</v>
       </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
+      <c r="N92"/>
       <c r="O92" t="s">
         <v>335</v>
       </c>
@@ -6854,9 +6666,7 @@
       <c r="M93">
         <v>23</v>
       </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
+      <c r="N93"/>
       <c r="O93" t="s">
         <v>338</v>
       </c>
@@ -6904,9 +6714,7 @@
       <c r="M94">
         <v>23</v>
       </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
+      <c r="N94"/>
       <c r="O94" t="s">
         <v>341</v>
       </c>
@@ -6954,9 +6762,7 @@
       <c r="M95">
         <v>34</v>
       </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
+      <c r="N95"/>
       <c r="O95" t="s">
         <v>344</v>
       </c>
@@ -7004,9 +6810,7 @@
       <c r="M96">
         <v>27</v>
       </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
+      <c r="N96"/>
       <c r="O96" t="s">
         <v>348</v>
       </c>
@@ -7054,9 +6858,7 @@
       <c r="M97">
         <v>43</v>
       </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
+      <c r="N97"/>
       <c r="O97" t="s">
         <v>351</v>
       </c>
@@ -7104,9 +6906,7 @@
       <c r="M98">
         <v>43</v>
       </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
+      <c r="N98"/>
       <c r="O98" t="s">
         <v>353</v>
       </c>
@@ -7154,9 +6954,7 @@
       <c r="M99">
         <v>23</v>
       </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
+      <c r="N99"/>
       <c r="O99" t="s">
         <v>357</v>
       </c>
@@ -7204,9 +7002,7 @@
       <c r="M100">
         <v>26</v>
       </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
+      <c r="N100"/>
       <c r="O100" t="s">
         <v>360</v>
       </c>
@@ -7254,9 +7050,7 @@
       <c r="M101">
         <v>420</v>
       </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
+      <c r="N101"/>
       <c r="O101" t="s">
         <v>364</v>
       </c>
@@ -7304,9 +7098,7 @@
       <c r="M102">
         <v>41</v>
       </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
+      <c r="N102"/>
       <c r="O102" t="s">
         <v>367</v>
       </c>
@@ -7354,9 +7146,7 @@
       <c r="M103">
         <v>23</v>
       </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
+      <c r="N103"/>
       <c r="O103" t="s">
         <v>371</v>
       </c>
@@ -7404,9 +7194,7 @@
       <c r="M104">
         <v>19</v>
       </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
+      <c r="N104"/>
       <c r="O104" t="s">
         <v>373</v>
       </c>
@@ -7454,9 +7242,7 @@
       <c r="M105">
         <v>22</v>
       </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
+      <c r="N105"/>
       <c r="O105" t="s">
         <v>376</v>
       </c>
@@ -7504,9 +7290,7 @@
       <c r="M106">
         <v>28</v>
       </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
+      <c r="N106"/>
       <c r="O106" t="s">
         <v>379</v>
       </c>
@@ -7554,9 +7338,7 @@
       <c r="M107">
         <v>26</v>
       </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
+      <c r="N107"/>
       <c r="O107" t="s">
         <v>381</v>
       </c>
@@ -7604,9 +7386,7 @@
       <c r="M108">
         <v>26</v>
       </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
+      <c r="N108"/>
       <c r="O108" t="s">
         <v>384</v>
       </c>
@@ -7654,9 +7434,7 @@
       <c r="M109">
         <v>40</v>
       </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
+      <c r="N109"/>
       <c r="O109" t="s">
         <v>387</v>
       </c>
@@ -7704,9 +7482,7 @@
       <c r="M110">
         <v>23</v>
       </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
+      <c r="N110"/>
       <c r="O110" t="s">
         <v>390</v>
       </c>
@@ -7754,9 +7530,7 @@
       <c r="M111">
         <v>21</v>
       </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
+      <c r="N111"/>
       <c r="O111" t="s">
         <v>393</v>
       </c>
@@ -7804,9 +7578,7 @@
       <c r="M112">
         <v>724</v>
       </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
+      <c r="N112"/>
       <c r="O112" t="s">
         <v>396</v>
       </c>
@@ -7815,6 +7587,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O6" r:id="rId1" display="https://www.chengde.gov.cn/shuju/web/dataServerView?id=000000006dfb4c3a016dfeac4ad0005e&amp;pageNum=1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
